--- a/tests/fixtures/AMSMC_employees_sample.xlsx
+++ b/tests/fixtures/AMSMC_employees_sample.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,30 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>01/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ravensworth, Cecily</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beaumont, Sylvie</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
     </row>
@@ -563,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +656,30 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>03/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Whitfield, Harold</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Whitfield, Harold</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
         </is>
       </c>
     </row>
@@ -646,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +772,30 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>04/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nakamura, Hiroshi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Beaumont, Sylvie</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/AMSMC_employees_sample.xlsx
+++ b/tests/fixtures/AMSMC_employees_sample.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,18 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ashgrove, Petra</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
         </is>
       </c>
     </row>
